--- a/data/trans_orig/P1420-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2012</t>
+          <t>Población con diagnóstico de hemorroides en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289513</t>
+          <t>290275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279977</t>
+          <t>279788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573893</t>
+          <t>573852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581107</t>
+          <t>581514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496698</t>
+          <t>497169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504592</t>
+          <t>504579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503841</t>
+          <t>503437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518415</t>
+          <t>517826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1004455</t>
+          <t>1003737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021614</t>
+          <t>1021875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1452,62 +1452,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5191</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6356</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318918</t>
+          <t>318913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658710</t>
+          <t>659875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>20210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366753</t>
+          <t>367696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371678</t>
+          <t>372613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384069</t>
+          <t>384254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743195</t>
+          <t>742723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>757058</t>
+          <t>756430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198106</t>
+          <t>198234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209398</t>
+          <t>209413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198677</t>
+          <t>199045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212615</t>
+          <t>212685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>402578</t>
+          <t>403098</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420074</t>
+          <t>419322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268248</t>
+          <t>269394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268782</t>
+          <t>269751</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277108</t>
+          <t>277113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542832</t>
+          <t>542814</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551034</t>
+          <t>551033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>12468</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>24549</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>651140</t>
+          <t>650320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660754</t>
+          <t>660787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>676508</t>
+          <t>675911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689713</t>
+          <t>689434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1331163</t>
+          <t>1332092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1347705</t>
+          <t>1348192</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22393</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766829</t>
+          <t>766769</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776907</t>
+          <t>776952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>807407</t>
+          <t>807587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819303</t>
+          <t>819297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579283</t>
+          <t>1579084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1594855</t>
+          <t>1594113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>72167</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66031</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102753</t>
+          <t>101819</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3388286</t>
+          <t>3387605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3409045</t>
+          <t>3408127</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3480578</t>
+          <t>3482931</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511595</t>
+          <t>3511910</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6879124</t>
+          <t>6880058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6915846</t>
+          <t>6916837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2016</t>
+          <t>Población con diagnóstico de hemorroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278200</t>
+          <t>279602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291034</t>
+          <t>291181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275261</t>
+          <t>275360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285753</t>
+          <t>286502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560171</t>
+          <t>559001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575555</t>
+          <t>575475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,47 +4432,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8226</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>984</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8495</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>982</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500548</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514589</t>
+          <t>514858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522100</t>
+          <t>522101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1016924</t>
+          <t>1018018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024677</t>
+          <t>1024675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312247</t>
+          <t>312701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331023</t>
+          <t>330441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646377</t>
+          <t>646391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654007</t>
+          <t>654009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356878</t>
+          <t>357151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367970</t>
+          <t>368021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366292</t>
+          <t>366732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381444</t>
+          <t>382295</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729017</t>
+          <t>728085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748092</t>
+          <t>748205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -5426,82 +5426,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6583</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6323</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212264</t>
+          <t>212004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424555</t>
+          <t>424546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252323</t>
+          <t>252758</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261325</t>
+          <t>261348</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263776</t>
+          <t>263621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272092</t>
+          <t>272121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520398</t>
+          <t>520075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532205</t>
+          <t>532924</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>17939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637803</t>
+          <t>637616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652369</t>
+          <t>652464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>673165</t>
+          <t>673355</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687013</t>
+          <t>687785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318505</t>
+          <t>1318168</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337333</t>
+          <t>1337006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>765258</t>
+          <t>764332</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776873</t>
+          <t>776847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>804313</t>
+          <t>805218</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820496</t>
+          <t>820696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1577654</t>
+          <t>1577179</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1595771</t>
+          <t>1595857</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22827</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>48388</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64010</t>
+          <t>60737</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>99935</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3345192</t>
+          <t>3345962</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371974</t>
+          <t>3371523</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3480532</t>
+          <t>3483805</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511359</t>
+          <t>3511231</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6838957</t>
+          <t>6836644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6878166</t>
+          <t>6875346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1420-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Provincia-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290275</t>
+          <t>290264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279788</t>
+          <t>279822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573852</t>
+          <t>573304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581514</t>
+          <t>581111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497169</t>
+          <t>497487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504579</t>
+          <t>504580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503437</t>
+          <t>503406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517826</t>
+          <t>517688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003737</t>
+          <t>1004761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021875</t>
+          <t>1021321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318913</t>
+          <t>318519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659875</t>
+          <t>659507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367696</t>
+          <t>366801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372613</t>
+          <t>371737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384254</t>
+          <t>384135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742723</t>
+          <t>743666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756430</t>
+          <t>757083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198234</t>
+          <t>197842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209413</t>
+          <t>209355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199045</t>
+          <t>198621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212685</t>
+          <t>213471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403098</t>
+          <t>402417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419322</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269394</t>
+          <t>269451</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269751</t>
+          <t>269433</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277113</t>
+          <t>277115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542814</t>
+          <t>542122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551033</t>
+          <t>551032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17942</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24549</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650320</t>
+          <t>650913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660787</t>
+          <t>660850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>675911</t>
+          <t>675884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689434</t>
+          <t>689215</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1332092</t>
+          <t>1331651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348192</t>
+          <t>1348246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766769</t>
+          <t>765531</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776952</t>
+          <t>776919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>807587</t>
+          <t>807647</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819297</t>
+          <t>819315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579084</t>
+          <t>1579575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1594113</t>
+          <t>1594257</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72167</t>
+          <t>73299</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65040</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>104383</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3387605</t>
+          <t>3386571</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3408127</t>
+          <t>3408622</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3482931</t>
+          <t>3481799</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511910</t>
+          <t>3512956</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6880058</t>
+          <t>6877494</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6916837</t>
+          <t>6915823</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279602</t>
+          <t>279802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291181</t>
+          <t>290918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275360</t>
+          <t>275820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286502</t>
+          <t>286339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559001</t>
+          <t>560632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575475</t>
+          <t>575276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514858</t>
+          <t>513578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522101</t>
+          <t>522106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1018018</t>
+          <t>1016791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024675</t>
+          <t>1024677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312701</t>
+          <t>313016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330441</t>
+          <t>331012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646391</t>
+          <t>647111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654009</t>
+          <t>654010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>21927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357151</t>
+          <t>357205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368021</t>
+          <t>367999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366732</t>
+          <t>365356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382295</t>
+          <t>381909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728085</t>
+          <t>729737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748205</t>
+          <t>747380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212004</t>
+          <t>212642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424546</t>
+          <t>424503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252758</t>
+          <t>252052</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261348</t>
+          <t>261367</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263621</t>
+          <t>263852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272121</t>
+          <t>272114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520075</t>
+          <t>520300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532924</t>
+          <t>532418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17939</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637616</t>
+          <t>639006</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652464</t>
+          <t>652647</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>673355</t>
+          <t>674049</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687785</t>
+          <t>686949</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318168</t>
+          <t>1319004</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337006</t>
+          <t>1337434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>20282</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27571</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764332</t>
+          <t>764362</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776847</t>
+          <t>776858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805218</t>
+          <t>805885</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820696</t>
+          <t>821483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1577179</t>
+          <t>1576882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1595857</t>
+          <t>1595735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60737</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63546</t>
+          <t>61837</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102248</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3345962</t>
+          <t>3345521</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371523</t>
+          <t>3371235</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3483805</t>
+          <t>3481473</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511231</t>
+          <t>3510908</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6836644</t>
+          <t>6840469</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6875346</t>
+          <t>6877055</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
